--- a/finanztracker_template.xlsx
+++ b/finanztracker_template.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ausgaben" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Einnahmen" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Daueraufträge" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Kategorien" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="README" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ausgaben" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Einnahmen" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Daueraufträge" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Kategorien" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Einstellungen" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,13 +22,30 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFF00"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A56DB"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00111111"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -40,7 +58,8 @@
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00888888"/>
+      <color rgb="00777777"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -49,19 +68,14 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFF00"/>
-      <sz val="16"/>
+      <color rgb="00AA3300"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="0061AFEF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00C0C8D8"/>
-      <sz val="11"/>
+      <i val="1"/>
+      <color rgb="00111111"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="35">
@@ -78,6 +92,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E8F0FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="000F3460"/>
       </patternFill>
     </fill>
@@ -229,11 +248,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00AAAAAA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000D1B2A"/>
       </patternFill>
     </fill>
   </fills>
@@ -263,114 +277,116 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="3"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -733,6 +749,230 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00E5C07B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="74" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Finanztracker Setup — Anleitung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="8" customHeight="1"/>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SCHRITT 1 — Diese Datei zu Google Drive hochladen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>→  Google Drive öffnen → '+Neu' → 'Datei hochladen' → diese Datei wählen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>→  Rechtsklick auf die Datei → 'Öffnen mit Google Tabellen'</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>→  Google konvertiert das Excel automatisch in ein Google Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="8" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SCHRITT 2 — Apps Script bereitstellen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>→  Im Google Sheet: Erweiterungen → Apps Script</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>→  Code.gs einfügen &amp; speichern  (Code findest du in der F-Tracker App unter 'Sheet einrichten')</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>→  Bereitstellen → Neue Bereitstellung → Web-App</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>→  Ausführen als: Ich  ·  Zugriff: Jeder (auch anonym)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>→  Berechtigungen bestätigen → Script-URL kopieren</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="8" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SCHRITT 3 — App verbinden</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>→  F-Tracker öffnen</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>→  Script-URL in das URL-Feld einfügen → 'Verbinden' klicken</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="8" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>WICHTIG</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>⚠  Spalten-Reihenfolge NICHT verändern — die App erwartet exakt diese Struktur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>⚠  Tabellenblattnamen (Ausgaben, Einnahmen, Daueraufträge, Kategorien, Einstellungen) nicht umbenennen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>⚠  Zeile 1 (Header) nicht löschen oder verändern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="8" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Sheet-Struktur Übersicht</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Ausgaben:      ID | Datum | Beschreibung | Kategorie | Betrag | Notiz | Deleted</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Einnahmen:     ID | Datum | Beschreibung | Kategorie | Betrag | Notiz | Deleted</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Daueraufträge: ID | Was | Kategorie | Betrag | Intervall | Tag | Kommentar | Aktiv | nextDate | startDate | endDate | lastBooked</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Kategorien:    ID | Name | Typ (ausgabe/einnahme) | Farbe (#HEX) | Sortierung</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Einstellungen: App-Einstellungen (automatisch von der App befüllt — nicht manuell bearbeiten)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="8" customHeight="1"/>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Kategorien anpassen</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>→  Im Sheet 'Kategorien' beliebige Zeilen hinzufügen/ändern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>→  Typ muss exakt 'ausgabe' oder 'einnahme' sein.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>→  Farbe: Hex-Code mit # z.B. #FF6B35</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00FF6B35"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -750,102 +990,102 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Beschreibung</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Kategorie</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Betrag</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Notiz</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Deleted</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>a001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Beispiel Supermarkt</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Poschte</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="5" t="n">
         <v>24.5</v>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>a002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>2026-01-02</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Beispiel Kaffee</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Snack</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="6" t="n">
         <v>3.5</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="003DBF6B"/>
@@ -865,82 +1105,82 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Beschreibung</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Kategorie</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Betrag</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Notiz</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Deleted</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>e001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Lohn Januar</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="5" t="n">
         <v>3127</v>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0061AFEF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -958,158 +1198,151 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Was</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Kategorie</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Betrag</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Intervall</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Tag</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Kommentar</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Aktiv</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>nextDate</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>startDate</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>endDate</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>lastBooked</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>d001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Miete</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Mieti</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="5" t="n">
         <v>1023</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>monatlich</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Wohnung</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr"/>
+      <c r="L2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>d002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Handy Abo</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Handy</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="6" t="n">
         <v>37.5</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>monatlich</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Swisscom</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr"/>
+      <c r="K3" s="6" t="inlineStr"/>
+      <c r="L3" s="6" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Gültige Intervall-Werte:</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>monatlich | wöchentlich | halbjährlich | jährlich | semestral</t>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Gültige Intervall-Werte: monatlich | wöchentlich | halbjährlich | jährlich | semestral</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C678DD"/>
@@ -1136,779 +1369,779 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Typ</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Farbe</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Sortierung</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>k001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Zmittag</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>#FF6B35</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>k002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Snack</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>#F7931E</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>k003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Ferien</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>#00D4AA</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>k004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Poschte</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>#4ECDC4</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="6" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>k005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Znacht</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>#FF6B6B</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="5" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>k006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Gschänk</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>#C678DD</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="6" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>k007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Chleider</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>#E06C75</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>k008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Technik</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>#61AFEF</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="6" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>k009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Mieti</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>#E5C07B</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="5" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>k010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Gsundheit</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>#56B6C2</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="6" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>k011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Internet</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>#98C379</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="5" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>k012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Handy</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>#ABB2BF</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="6" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>k013</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Alkohol</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>#D19A66</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="5" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>k014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Essen in Reschti</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>#FF8FAB</t>
         </is>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="6" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>k015</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Rudern</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>#5E81F4</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="5" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>k016</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Bildung</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>#A8E063</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="6" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>k017</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Verlochet</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>#FD6E6A</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="5" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>k018</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>SBB</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
         <is>
           <t>#E63946</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="6" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>k019</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Möbel o.Ä.</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>#8B8FA8</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="5" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>k020</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Gipfeli</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>#F6C90E</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="6" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>k021</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Buch</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>#7BC8A4</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="5" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>k022</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Sport</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D23" s="26" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>#FF9F43</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="6" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>k023</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Freiziit</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D24" s="27" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D24" s="30" t="inlineStr">
         <is>
           <t>#54A0FF</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="5" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>k024</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Diverses</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>ausgabe</t>
-        </is>
-      </c>
-      <c r="D25" s="28" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>ausgabe</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
         <is>
           <t>#888888</t>
         </is>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="6" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>k025</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>einnahme</t>
         </is>
       </c>
-      <c r="D26" s="29" t="inlineStr">
+      <c r="D26" s="32" t="inlineStr">
         <is>
           <t>#C8F53C</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="5" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>k026</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Twint</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>einnahme</t>
         </is>
       </c>
-      <c r="D27" s="30" t="inlineStr">
+      <c r="D27" s="33" t="inlineStr">
         <is>
           <t>#00C9A7</t>
         </is>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="6" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>k027</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Schenkung</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>einnahme</t>
         </is>
       </c>
-      <c r="D28" s="31" t="inlineStr">
+      <c r="D28" s="34" t="inlineStr">
         <is>
           <t>#FFD93D</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" s="5" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>k028</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Übertrag</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>einnahme</t>
         </is>
       </c>
-      <c r="D29" s="32" t="inlineStr">
+      <c r="D29" s="35" t="inlineStr">
         <is>
           <t>#95E1D3</t>
         </is>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="6" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>k029</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Diverses</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>einnahme</t>
         </is>
       </c>
-      <c r="D30" s="33" t="inlineStr">
+      <c r="D30" s="36" t="inlineStr">
         <is>
           <t>#AAAAAA</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" s="5" t="n">
         <v>29</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>k030</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Kaution</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>einnahme</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>#4ECDC4</t>
         </is>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="6" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1917,219 +2150,73 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00E5C07B"/>
+    <tabColor rgb="00888888"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="72" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="34" t="inlineStr">
-        <is>
-          <t>Finanztracker Setup — Anleitung</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
-        <is>
-          <t>SCHRITT 1 — Diese Datei zu Google Drive hochladen</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="36" t="inlineStr">
-        <is>
-          <t>→  Google Drive öffnen → '+Neu' → 'Datei hochladen' → diese Datei wählen</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="36" t="inlineStr">
-        <is>
-          <t>→  Rechtsklick auf die Datei → 'Öffnen mit Google Tabellen'</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="36" t="inlineStr">
-        <is>
-          <t>→  Google konvertiert das Excel automatisch in ein Google Sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="8" customHeight="1"/>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="35" t="inlineStr">
-        <is>
-          <t>SCHRITT 2 — Apps Script bereitstellen</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="36" t="inlineStr">
-        <is>
-          <t>→  Im Google Sheet: Erweiterungen → Apps Script</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="36" t="inlineStr">
-        <is>
-          <t>→  Code.gs einfügen &amp; speichern  (Code findest du in der F-Tracker App unter Einrichten)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="36" t="inlineStr">
-        <is>
-          <t>→  Bereitstellen → Neue Bereitstellung → Web-App</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="36" t="inlineStr">
-        <is>
-          <t>→  Ausführen als: Ich  ·  Zugriff: Jeder (auch anonym)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="36" t="inlineStr">
-        <is>
-          <t>→  Berechtigungen bestätigen → Script-URL kopieren</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="8" customHeight="1"/>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="35" t="inlineStr">
-        <is>
-          <t>SCHRITT 3 — App verbinden</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="36" t="inlineStr">
-        <is>
-          <t>→  F-Tracker öffnen</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="36" t="inlineStr">
-        <is>
-          <t>→  Script-URL in das URL-Feld einfügen → 'Verbinden' klicken</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="8" customHeight="1"/>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="35" t="inlineStr">
-        <is>
-          <t>WICHTIG</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="36" t="inlineStr">
-        <is>
-          <t>⚠  Spalten-Reihenfolge NICHT verändern — die App erwartet exakt diese Struktur.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="36" t="inlineStr">
-        <is>
-          <t>⚠  Tabellenblattnamen (Ausgaben, Einnahmen, Daueraufträge, Kategorien) nicht umbenennen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="36" t="inlineStr">
-        <is>
-          <t>⚠  Zeile 1 (Header) nicht löschen oder verändern.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="8" customHeight="1"/>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="35" t="inlineStr">
-        <is>
-          <t>Sheet-Struktur Übersicht</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="36" t="inlineStr">
-        <is>
-          <t>Ausgaben:      ID | Datum | Beschreibung | Kategorie | Betrag | Notiz | Deleted</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="36" t="inlineStr">
-        <is>
-          <t>Einnahmen:     ID | Datum | Beschreibung | Kategorie | Betrag | Notiz | Deleted</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="36" t="inlineStr">
-        <is>
-          <t>Daueraufträge: ID | Was | Kategorie | Betrag | Intervall | Tag | Kommentar | Aktiv | nextDate | startDate | endDate | lastBooked</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="36" t="inlineStr">
-        <is>
-          <t>Kategorien:    ID | Name | Typ (ausgabe/einnahme) | Farbe (#HEX) | Sortierung</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="8" customHeight="1"/>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="35" t="inlineStr">
-        <is>
-          <t>Kategorien anpassen</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="36" t="inlineStr">
-        <is>
-          <t>→  Im Sheet 'Kategorien' beliebige Zeilen hinzufügen/ändern.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="36" t="inlineStr">
-        <is>
-          <t>→  Typ muss exakt 'ausgabe' oder 'einnahme' sein.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="36" t="inlineStr">
-        <is>
-          <t>→  Farbe: Hex-Code mit # z.B. #FF6B35</t>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Schlüssel</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Wert (JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>ft_profile_v1</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>{"ft_profile_v1": true, "userName": "", "theme": "", "lohnTag": 25, "sparziel": 0, "mSparziel": 0, "pinnedTabs": [], "homeWidgets": null, "notifSettings": {}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>HINWEIS:</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>→  Dieses Tabellenblatt wird automatisch von der F-Tracker App befüllt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>→  Bitte keine manuellen Änderungen vornehmen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="38" t="inlineStr">
+        <is>
+          <t>→  Gespeichert werden: Kacheln-Layout, Tab-Pins, Name, Theme, Einstellungen.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/finanztracker_template.xlsx
+++ b/finanztracker_template.xlsx
@@ -12,7 +12,9 @@
     <sheet name="Einnahmen" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Daueraufträge" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Kategorien" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Einstellungen" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Aktien" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Trades" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Einstellungen" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="74" customWidth="1" min="1" max="1"/>
@@ -879,7 +881,7 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>⚠  Tabellenblattnamen (Ausgaben, Einnahmen, Daueraufträge, Kategorien, Einstellungen) nicht umbenennen.</t>
+          <t>⚠  Tabellenblattnamen (Ausgaben, Einnahmen, Daueraufträge, Kategorien, Einstellungen, Aktien, Trades) nicht umbenennen.</t>
         </is>
       </c>
     </row>
@@ -901,14 +903,14 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Ausgaben:      ID | Datum | Beschreibung | Kategorie | Betrag | Notiz | Deleted</t>
+          <t>Ausgaben:      ID | Datum | Beschreibung | Kategorie | Betrag | Notiz | Deleted | isFixkosten</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Einnahmen:     ID | Datum | Beschreibung | Kategorie | Betrag | Notiz | Deleted</t>
+          <t>Einnahmen:     ID | Datum | Beschreibung | Kategorie | Betrag | Notiz | Deleted | isLohn</t>
         </is>
       </c>
     </row>
@@ -933,32 +935,82 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="8" customHeight="1"/>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Aktien:        ID | Titel | ISIN | Ticker (Yahoo Finance) | Währung | Deleted</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Trades:        ID | AktieID | Typ (kauf/verkauf) | Datum | Anzahl | Preis/Stk | Währung | Courtage | Gesamt | Deleted</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Kategorien anpassen</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>→  Im Sheet 'Kategorien' beliebige Zeilen hinzufügen/ändern.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>→  Typ muss exakt 'ausgabe' oder 'einnahme' sein.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>→  Im Sheet 'Kategorien' beliebige Zeilen hinzufügen/ändern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>→  Typ muss exakt 'ausgabe' oder 'einnahme' sein.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
           <t>→  Farbe: Hex-Code mit # z.B. #FF6B35</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="8" customHeight="1"/>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Aktien-Ticker (Yahoo Finance Symbole)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>→  Schweizer Aktien:  ZURN.SW, ABBN.SW, NESN.SW, UBSG.SW  (Suffix .SW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>→  ETFs auf XETRA:   IQQE.DE, CSSMI.SW  (Suffix .DE oder .SW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>→  Schwedische Aktien: SAAB-B.ST  (Suffix .ST)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>→  US-Aktien:         AAPL, MSFT  (kein Suffix)</t>
         </is>
       </c>
     </row>
@@ -2153,6 +2205,962 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00F7C948"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Titel</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>ISIN</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Ticker (Yahoo)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Währung</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Deleted</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>st_001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Zurich Insurance N</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>CH0011075394</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>ZURN.SW</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>st_002</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>iSh EURSTx50 DE EUR D</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>DE0005933956</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>IQQE.DE</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>st_003</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>iSh SLI CH CHF D</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>CH0031768937</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>CSSLI.SW</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>st_004</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>UBSETF SMI CHF DIS</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>CH0017142719</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CSSMI.SW</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>st_005</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Nestlé N</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>CH0038863350</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>NESN.SW</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>st_006</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>UBS Group N</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>CH0244767585</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>UBSG.SW</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>st_007</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>UBS Sol. China Tech UCITS USD</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>LU2265794276</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>UBCT.SW</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>st_008</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>SAAB ORD</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>SE0021921269</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>SAAB-B.ST</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>st_009</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>ABB Ltd N</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>ABBN.SW</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Ticker-Beispiele: .SW = Schweiz, .DE = XETRA, .ST = Stockholm, kein Suffix = USA</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0056B6C2"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>AktieID</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Typ</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Anzahl</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Preis/Stk</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Währung</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Courtage</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Gesamt</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Deleted</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>tr_001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>st_001</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>kauf</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>622</v>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>2488</v>
+      </c>
+      <c r="J2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>tr_002</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>st_001</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>verkauf</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>571.2</v>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>1142.4</v>
+      </c>
+      <c r="J3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>tr_003</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>st_002</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>kauf</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>47.915</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1485.37</v>
+      </c>
+      <c r="J4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>tr_004</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>st_002</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>verkauf</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>981</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>tr_005</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>st_003</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>kauf</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>193.4</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>1547.2</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>tr_006</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>st_003</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>verkauf</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>214.55</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>429.1</v>
+      </c>
+      <c r="J7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>tr_007</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>st_004</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>kauf</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1122</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>tr_008</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>st_004</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>verkauf</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1316.95</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>13169.5</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>tr_009</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>st_005</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>kauf</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1980</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>tr_010</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>st_006</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>kauf</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>1075</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>tr_011</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>st_006</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>verkauf</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>484.5</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>tr_012</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>st_007</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>kauf</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>176</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1619.2</v>
+      </c>
+      <c r="J13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>tr_013</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>st_008</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>kauf</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>572.4</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>16027.2</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>tr_014</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>st_009</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>kauf</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>662.2</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Typ: 'kauf' oder 'verkauf'  |  AktieID muss mit ID im Aktien-Sheet übereinstimmen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00888888"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
